--- a/public/TagPhuTro.xlsx
+++ b/public/TagPhuTro.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24131"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPDQ-SAM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\truonghoaisam\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F001E333-2A32-4D9E-A92A-DF83D95CB12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="QGC1TK1" sheetId="16" r:id="rId1"/>
@@ -28,7 +27,7 @@
     <sheet name="NH2OngKhoiVaQuaGioTK2" sheetId="14" r:id="rId13"/>
     <sheet name="KKKTK2" sheetId="22" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="487">
   <si>
     <t>Tag0</t>
   </si>
@@ -1500,12 +1499,15 @@
   </si>
   <si>
     <t>Motor_bearing_temperature_out_232A_1</t>
+  </si>
+  <si>
+    <t>TK_2SWH_AI098</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1998,7 +2000,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D456FA42-BF76-4705-BCE9-D0366D5B2157}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2368,7 +2370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{510E56EA-4437-43D9-9C11-D4D287FDE4B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2812,7 +2814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9B4B2D-2EC7-4071-AAFE-1707262B4794}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3256,7 +3258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F53956D-3759-4888-926F-F28C1176A235}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3616,7 +3618,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74BED112-8A91-4C3B-8A9F-9CF2C737A748}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4058,7 +4060,7 @@
         <v>46</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>319</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -4078,7 +4080,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6ABC56F-C1A4-42C7-B064-5CBB327D5824}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4516,7 +4518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92A6C077-5FFE-4310-8BAA-FEB8A9BA7488}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="F1:J24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4886,7 +4888,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3038E241-611E-4F02-AC86-560BDDAA4E93}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5330,7 +5332,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85908779-5337-4E63-B5A7-60DCE5794979}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5774,7 +5776,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CBF0E9-EF57-473A-B178-4E56AAAB53E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6133,7 +6135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84143BD3-351E-4852-9626-BFEDD75F1279}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6595,7 +6597,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79CD02E9-3C5D-4ED2-8B52-FEDF29A16E1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7033,7 +7035,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E269D4A-8DD8-4FA0-83CE-2B7135C8BAD7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7499,7 +7501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76AEB321-E204-4CD0-9AEB-D74C4A635A1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
